--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487924_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487924_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5001</v>
+        <v>5.194</v>
       </c>
       <c r="E2" t="n">
-        <v>3.019</v>
+        <v>2.977</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4811</v>
+        <v>2.2169</v>
       </c>
       <c r="G2" t="n">
         <v>3.1395</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3033</v>
+        <v>-0.6095</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.46</v>
+        <v>-0.5019</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1567</v>
+        <v>-0.1076</v>
       </c>
       <c r="V2" t="n">
         <v>1.4152</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6983</v>
+        <v>3.8852</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7952</v>
+        <v>3.7767</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.097</v>
+        <v>0.1086</v>
       </c>
       <c r="G3" t="n">
         <v>3.0423</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.6795</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3948</v>
+        <v>-0.4133</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4717</v>
+        <v>-0.2661</v>
       </c>
       <c r="V3" t="n">
         <v>0.6899</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8368</v>
+        <v>2.8157</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9318</v>
+        <v>2.7052</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.095</v>
+        <v>0.1105</v>
       </c>
       <c r="G4" t="n">
         <v>0.765</v>
@@ -766,13 +766,13 @@
         <v>2.7055</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2175</v>
+        <v>-1.2386</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5658</v>
+        <v>-0.7924</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.4462</v>
       </c>
       <c r="V4" t="n">
         <v>0.5838</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9752</v>
+        <v>0.3476</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3444</v>
+        <v>-0.019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6308</v>
+        <v>0.3666</v>
       </c>
       <c r="G5" t="n">
         <v>0.3342</v>
@@ -844,13 +844,13 @@
         <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0354</v>
+        <v>0.4078</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1553</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5167</v>
+        <v>0.2525</v>
       </c>
       <c r="V5" t="n">
         <v>0.23</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. PIEKUS</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9405</v>
+        <v>-0.0368</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8102</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8231</v>
+        <v>-0.847</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8494</v>
+        <v>2.0545</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2453</v>
+        <v>1.674</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6041</v>
+        <v>0.3804</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4325</v>
+        <v>4.5939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4325</v>
+        <v>2.2214</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3725</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.282</v>
+        <v>-2.5394</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6778</v>
+        <v>-0.5474</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6041</v>
+        <v>-1.9921</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2846</v>
+        <v>-1.0507</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4907</v>
+        <v>-0.6619</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2061</v>
+        <v>-0.3888</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.044</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0598</v>
+        <v>-0.8129</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9842</v>
+        <v>0.1279</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1685</v>
+        <v>-1.4499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0534</v>
+        <v>-0.7699</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1151</v>
+        <v>-0.6801</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1359</v>
+        <v>-0.5395</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0576</v>
+        <v>-0.5697</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0784</v>
+        <v>0.0302</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0326</v>
+        <v>-0.9105</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0041</v>
+        <v>-0.2002</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0367</v>
+        <v>-0.7103</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6694</v>
+        <v>-0.9</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1957</v>
+        <v>-0.5034</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4736</v>
+        <v>-0.3966</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0526</v>
+        <v>-0.8972</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0924</v>
+        <v>-0.0598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0398</v>
+        <v>-0.8374</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4499</v>
+        <v>0.1685</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7699</v>
+        <v>0.0534</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6801</v>
+        <v>0.1151</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5395</v>
+        <v>0.1359</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5697</v>
+        <v>0.0576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0302</v>
+        <v>0.0784</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9105</v>
+        <v>0.0326</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2002</v>
+        <v>-0.0041</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7103</v>
+        <v>0.0367</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2676</v>
+        <v>-0.5226</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7829</v>
+        <v>-0.1957</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4847</v>
+        <v>-0.3268</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>P. PIEKUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3746</v>
+        <v>-2.0372</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0284</v>
+        <v>-0.2728</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3461</v>
+        <v>-1.7644</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0545</v>
+        <v>-0.8494</v>
       </c>
       <c r="H9" t="n">
-        <v>1.674</v>
+        <v>-0.2453</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3804</v>
+        <v>-0.6041</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5939</v>
+        <v>0.4325</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2214</v>
+        <v>0.4325</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3725</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5394</v>
+        <v>-1.282</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5474</v>
+        <v>-0.6778</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9921</v>
+        <v>-0.6041</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3885</v>
+        <v>0.1879</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5006</v>
+        <v>0.3353</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8879</v>
+        <v>-0.1474</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8986</v>
+        <v>-3.0426</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5088</v>
+        <v>-1.2712</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3898</v>
+        <v>-1.7714</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7525</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2511</v>
+        <v>-0.3952</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5905</v>
+        <v>-0.3528</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3393</v>
+        <v>-0.0423</v>
       </c>
       <c r="V10" t="n">
         <v>0.3538</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.558</v>
+        <v>-5.423</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8174</v>
+        <v>-5.3888</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2594</v>
+        <v>-0.0342</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3497</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3353</v>
+        <v>-0.2003</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3171</v>
+        <v>0.0235</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8579000000000008</v>
+        <v>0.1206999999999994</v>
       </c>
       <c r="E12" t="n">
-        <v>1.466199999999999</v>
+        <v>2.444599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3241</v>
+        <v>-2.3239</v>
       </c>
       <c r="G12" t="n">
         <v>2.1025</v>
@@ -1390,13 +1390,13 @@
         <v>15.6089</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.979100000000001</v>
+        <v>-5.0007</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1334</v>
+        <v>-3.1546</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.845899999999999</v>
+        <v>-1.8458</v>
       </c>
       <c r="V12" t="n">
         <v>0.9377000000000003</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4761</v>
+        <v>4.861</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7645</v>
+        <v>4.443</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7116</v>
+        <v>0.418</v>
       </c>
       <c r="G13" t="n">
         <v>3.7481</v>
@@ -1468,13 +1468,13 @@
         <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1869</v>
+        <v>1.5718</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5153</v>
+        <v>0.1939</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6715</v>
+        <v>1.378</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2914</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0333</v>
+        <v>2.9809</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2833</v>
+        <v>4.1433</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>-1.1624</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0326</v>
+        <v>3.1901</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4883</v>
+        <v>-0.452</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5209</v>
+        <v>3.6421</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3553</v>
+        <v>6.2806</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4517</v>
+        <v>1.4303</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0963</v>
+        <v>4.8504</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.388</v>
+        <v>-3.0905</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0366</v>
+        <v>-1.8823</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4245</v>
+        <v>-1.2083</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8984</v>
+        <v>-0.1468</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.199</v>
+        <v>-0.0562</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0974</v>
+        <v>-0.0906</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8594</v>
+        <v>2.0714</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2861</v>
+        <v>0.4976</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4267</v>
+        <v>1.5739</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1901</v>
+        <v>-0.0326</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.452</v>
+        <v>0.4883</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6421</v>
+        <v>-0.5209</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2806</v>
+        <v>0.3553</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4303</v>
+        <v>0.4517</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8504</v>
+        <v>-0.0963</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0905</v>
+        <v>-0.388</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8823</v>
+        <v>0.0366</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2083</v>
+        <v>-0.4245</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2683</v>
+        <v>0.9365</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9134</v>
+        <v>0.0153</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3549</v>
+        <v>0.9212</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6954</v>
+        <v>1.7685</v>
       </c>
       <c r="E16" t="n">
-        <v>0.338</v>
+        <v>1.0881</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3574</v>
+        <v>0.6804</v>
       </c>
       <c r="G16" t="n">
         <v>1.2226</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7353</v>
+        <v>0.3378</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7177</v>
+        <v>0.0324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0176</v>
+        <v>0.3054</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4459</v>
+        <v>-0.2417</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4935</v>
+        <v>0.0268</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9393</v>
+        <v>-0.2686</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.3811</v>
+        <v>2.1115</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.8577</v>
+        <v>0.1154</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5233</v>
+        <v>1.9962</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.3722</v>
+        <v>3.7285</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.0205</v>
+        <v>1.2384</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6482</v>
+        <v>2.4901</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0088</v>
+        <v>-1.6169</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8373</v>
+        <v>-1.123</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1716</v>
+        <v>-0.4939</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6244</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-5.2029</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7055</v>
+        <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>4.9726</v>
+        <v>0.6842</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>-0.1261</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4726</v>
+        <v>0.8104</v>
       </c>
       <c r="V17" t="n">
-        <v>0.23</v>
+        <v>-0.1238</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4599</v>
+        <v>1.6275</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1176</v>
+        <v>-0.6288</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6133</v>
+        <v>-0.5062</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5043</v>
+        <v>-0.1226</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9335</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.308</v>
+        <v>0.1809</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1338</v>
+        <v>-0.0266</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1742</v>
+        <v>0.2075</v>
       </c>
       <c r="V18" t="n">
         <v>0.7076</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2149</v>
+        <v>-1.5992</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1519</v>
+        <v>0.4848</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.063</v>
+        <v>-2.0841</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1115</v>
+        <v>-0.9373</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1154</v>
+        <v>0.0171</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9962</v>
+        <v>-0.9544</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7285</v>
+        <v>0.0548</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2384</v>
+        <v>-0.0236</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4901</v>
+        <v>0.0784</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6169</v>
+        <v>-0.9921</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.123</v>
+        <v>0.0407</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4939</v>
+        <v>-1.0328</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9137</v>
+        <v>1.4568</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.2029</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.289</v>
+        <v>-0.1375</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3049</v>
+        <v>0.4301</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0159</v>
+        <v>-0.5676</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1238</v>
+        <v>-1.9813</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7513</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4478</v>
+        <v>-1.6034</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0214</v>
+        <v>-1.2357</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4264</v>
+        <v>-0.3677</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2913</v>
@@ -2014,13 +2014,13 @@
         <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4273</v>
+        <v>0.2717</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3882</v>
+        <v>0.1738</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7945</v>
+        <v>-2.3035</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3777</v>
+        <v>-3.7438</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1721</v>
+        <v>1.4402</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9373</v>
+        <v>-5.3811</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0171</v>
+        <v>-4.8577</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9544</v>
+        <v>-0.5233</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0548</v>
+        <v>-3.3722</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0236</v>
+        <v>-4.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0784</v>
+        <v>0.6482</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9921</v>
+        <v>-2.0088</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0407</v>
+        <v>-0.8373</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0328</v>
+        <v>-1.1716</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4568</v>
+        <v>2.7055</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3327</v>
+        <v>2.2232</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3229</v>
+        <v>1.2497</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9813</v>
+        <v>0.23</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9813</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0773</v>
+        <v>-4.4472</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4453</v>
+        <v>-2.8739</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.632</v>
+        <v>-1.5733</v>
       </c>
       <c r="G22" t="n">
         <v>-1.799</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4273</v>
+        <v>0.0574</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3882</v>
+        <v>-0.0405</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8579999999999988</v>
+        <v>0.8579999999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>2.324199999999999</v>
+        <v>2.324000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>-1.4662</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.102500000000001</v>
+        <v>-2.1025</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.0618</v>
+        <v>-4.061800000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9595</v>
+        <v>1.959499999999999</v>
       </c>
       <c r="J23" t="n">
         <v>13.3099</v>
@@ -2239,7 +2239,7 @@
         <v>-8.347799999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0812</v>
+        <v>-2.081199999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.6089</v>
@@ -2248,13 +2248,13 @@
         <v>13.5275</v>
       </c>
       <c r="S23" t="n">
-        <v>5.979200000000001</v>
+        <v>5.9792</v>
       </c>
       <c r="T23" t="n">
         <v>1.8458</v>
       </c>
       <c r="U23" t="n">
-        <v>4.1332</v>
+        <v>4.1336</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9376000000000002</v>
